--- a/templates/SRI_OS_ข้อมูลตั้งต้น.xlsx
+++ b/templates/SRI_OS_ข้อมูลตั้งต้น.xlsx
@@ -973,7 +973,7 @@
       <formula1>"Management,Manager,User"</formula1>
     </dataValidation>
     <dataValidation sqref="D6:D400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="เลือกจากรายการเท่านั้น" type="list">
-      <formula1>"SRI Corporation,SRI Holding,SRI Capital,ธนากร,ธนวินท์,เบ็ญจพร"</formula1>
+      <formula1>"SRI Corporation,สุธี,ธนากร,ธนวินท์,เบ็ญจพร,สุดจิตต์"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1200,7 +1200,7 @@
       <formula1>"bank,petty_cash,cashier_cheque,credit_card,other"</formula1>
     </dataValidation>
     <dataValidation sqref="E6:E400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="เลือกจากรายการเท่านั้น" type="list">
-      <formula1>"SRI Corporation,SRI Holding,SRI Capital,ธนากร,ธนวินท์,เบ็ญจพร"</formula1>
+      <formula1>"SRI Corporation,สุธี,ธนากร,ธนวินท์,เบ็ญจพร,สุดจิตต์"</formula1>
     </dataValidation>
     <dataValidation sqref="H6:H400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="เลือกจากรายการเท่านั้น" type="list">
       <formula1>"ใช่,ไม่ใช่"</formula1>
@@ -1394,7 +1394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1411,6 +1411,7 @@
     <col width="22" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1440,60 +1441,65 @@
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>หมวด *</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
+          <t>หมวดใหญ่ *</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>หมวดย่อย *</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>ประเภท</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>ที่ตั้ง</t>
         </is>
       </c>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>ถือในชื่อ *</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="H4" s="13" t="inlineStr">
         <is>
           <t>ผู้รับผลประโยชน์</t>
         </is>
       </c>
-      <c r="H4" s="13" t="inlineStr">
+      <c r="I4" s="13" t="inlineStr">
         <is>
           <t>สัดส่วน %</t>
         </is>
       </c>
-      <c r="I4" s="12" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>ต้นทุน *</t>
         </is>
       </c>
-      <c r="J4" s="13" t="inlineStr">
+      <c r="K4" s="13" t="inlineStr">
         <is>
           <t>มูลค่าปัจจุบัน</t>
         </is>
       </c>
-      <c r="K4" s="13" t="inlineStr">
+      <c r="L4" s="13" t="inlineStr">
         <is>
           <t>แหล่งเงินทุน</t>
         </is>
       </c>
-      <c r="L4" s="13" t="inlineStr">
+      <c r="M4" s="13" t="inlineStr">
         <is>
           <t>วันที่ได้มา</t>
         </is>
       </c>
-      <c r="M4" s="12" t="inlineStr">
+      <c r="N4" s="12" t="inlineStr">
         <is>
           <t>สถานะ *</t>
         </is>
       </c>
-      <c r="N4" s="13" t="inlineStr">
+      <c r="O4" s="13" t="inlineStr">
         <is>
           <t>ผู้ดูแล</t>
         </is>
@@ -1512,60 +1518,65 @@
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>ขายฝาก / จำนอง / ปล่อยเช่า / รอขาย / Project / รอปรับปรุง</t>
+          <t>Businesses / Real Estate / Paper Asset / Commodity &amp; Cash</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
+          <t>ต้องอยู่ใต้หมวดใหญ่ที่เลือก</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
           <t>คอนโด / บ้าน / ที่ดิน / อาคารพาณิชย์</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="F5" s="14" t="inlineStr">
         <is>
           <t>จังหวัด หรือที่อยู่ย่อ</t>
         </is>
       </c>
-      <c r="F5" s="14" t="inlineStr">
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>ผู้ถือกรรมสิทธิ์ตามเอกสาร</t>
         </is>
       </c>
-      <c r="G5" s="14" t="inlineStr">
+      <c r="H5" s="14" t="inlineStr">
         <is>
           <t>ถ้าต่างจากผู้ถือ</t>
         </is>
       </c>
-      <c r="H5" s="14" t="inlineStr">
+      <c r="I5" s="14" t="inlineStr">
         <is>
           <t>100 ถ้าถือคนเดียว</t>
         </is>
       </c>
-      <c r="I5" s="14" t="inlineStr">
+      <c r="J5" s="14" t="inlineStr">
         <is>
           <t>เงินที่จ่ายไปจริงทั้งหมด รวมค่าโอน</t>
         </is>
       </c>
-      <c r="J5" s="14" t="inlineStr">
-        <is>
-          <t>ราคาประเมิน ถ้าไม่มีปล่อยว่าง ระบบใช้ต้นทุน</t>
-        </is>
-      </c>
       <c r="K5" s="14" t="inlineStr">
         <is>
+          <t>ราคาประเมิน · **ต่ำกว่าต้นทุนได้** ถ้าราคาตก ไม่ต้องดัดให้เท่าทุน</t>
+        </is>
+      </c>
+      <c r="L5" s="14" t="inlineStr">
+        <is>
           <t>เช่น ทุนป๊า / เงินหมุนจาก...</t>
         </is>
       </c>
-      <c r="L5" s="14" t="inlineStr">
+      <c r="M5" s="14" t="inlineStr">
         <is>
           <t>วว/ดด/ปปปป</t>
         </is>
       </c>
-      <c r="M5" s="14" t="inlineStr">
+      <c r="N5" s="14" t="inlineStr">
         <is>
           <t>ดำเนินอยู่ / ไม่ได้ใช้ / ขายแล้ว / ไถ่ถอนแล้ว</t>
         </is>
       </c>
-      <c r="N5" s="14" t="inlineStr">
+      <c r="O5" s="14" t="inlineStr">
         <is>
           <t>คนในทีมที่ดูแลทรัพย์นี้</t>
         </is>
@@ -1584,54 +1595,59 @@
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>ขายฝาก</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
+          <t>ขายฝาก / รับจำนอง</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
           <t>คอนโด</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>สมุทรปราการ</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>เบ็ญจพร</t>
         </is>
       </c>
-      <c r="G6" s="15" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>SRI Corporation</t>
         </is>
       </c>
-      <c r="H6" s="15" t="n">
+      <c r="I6" s="15" t="n">
         <v>100</v>
-      </c>
-      <c r="I6" s="15" t="n">
-        <v>1800000</v>
       </c>
       <c r="J6" s="15" t="n">
         <v>1800000</v>
       </c>
-      <c r="K6" s="15" t="inlineStr">
+      <c r="K6" s="15" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="L6" s="15" t="inlineStr">
         <is>
           <t>เงินหมุนจากเปรมสิริ</t>
         </is>
       </c>
-      <c r="L6" s="15" t="inlineStr">
+      <c r="M6" s="15" t="inlineStr">
         <is>
           <t>02/12/2025</t>
         </is>
       </c>
-      <c r="M6" s="15" t="inlineStr">
+      <c r="N6" s="15" t="inlineStr">
         <is>
           <t>ดำเนินอยู่</t>
         </is>
       </c>
-      <c r="N6" s="15" t="inlineStr">
+      <c r="O6" s="15" t="inlineStr">
         <is>
           <t>วิน</t>
         </is>
@@ -1650,46 +1666,51 @@
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
           <t>ปล่อยเช่า</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>คอนโด</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>กรุงเทพฯ</t>
         </is>
       </c>
-      <c r="F7" s="15" t="inlineStr">
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>ธนากร</t>
         </is>
       </c>
-      <c r="G7" s="15" t="inlineStr"/>
-      <c r="H7" s="15" t="n">
+      <c r="H7" s="15" t="inlineStr"/>
+      <c r="I7" s="15" t="n">
         <v>100</v>
       </c>
-      <c r="I7" s="15" t="n">
+      <c r="J7" s="15" t="n">
         <v>2450000</v>
       </c>
-      <c r="J7" s="15" t="n">
+      <c r="K7" s="15" t="n">
         <v>2780000</v>
       </c>
-      <c r="K7" s="15" t="inlineStr"/>
-      <c r="L7" s="15" t="inlineStr">
+      <c r="L7" s="15" t="inlineStr"/>
+      <c r="M7" s="15" t="inlineStr">
         <is>
           <t>30/09/2025</t>
         </is>
       </c>
-      <c r="M7" s="15" t="inlineStr">
+      <c r="N7" s="15" t="inlineStr">
         <is>
           <t>ดำเนินอยู่</t>
         </is>
       </c>
-      <c r="N7" s="15" t="inlineStr">
+      <c r="O7" s="15" t="inlineStr">
         <is>
           <t>แพทตี้</t>
         </is>
@@ -1697,20 +1718,23 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
   </mergeCells>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation sqref="C6:C400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="เลือกจากรายการเท่านั้น" type="list">
-      <formula1>"ขายฝาก,จำนอง,ปล่อยเช่า,รอขาย,Project,รอปรับปรุง,เงินให้กู้ยืม"</formula1>
+      <formula1>"Businesses,Real Estate,Paper Asset,Commodity &amp; Cash"</formula1>
     </dataValidation>
-    <dataValidation sqref="F6:F400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="เลือกจากรายการเท่านั้น" type="list">
-      <formula1>"SRI Corporation,SRI Holding,SRI Capital,ธนากร,ธนวินท์,เบ็ญจพร"</formula1>
+    <dataValidation sqref="D6:D400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="เลือกจากรายการเท่านั้น" type="list">
+      <formula1>"เงินลงทุนในกิจการ,บริษัทในเครือ,ปล่อยเช่า,รอขาย,โครงการระหว่างพัฒนา,รอปรับปรุง,ขายฝาก / รับจำนอง,หุ้น,ETF,กองทุน,พันธบัตร / หุ้นกู้,สัญญาเงินให้กู้ยืม,ทองคำ,คริปโต,เงินสดและเงินฝาก"</formula1>
     </dataValidation>
     <dataValidation sqref="G6:G400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="เลือกจากรายการเท่านั้น" type="list">
-      <formula1>"SRI Corporation,SRI Holding,SRI Capital,ธนากร,ธนวินท์,เบ็ญจพร"</formula1>
+      <formula1>"SRI Corporation,สุธี,ธนากร,ธนวินท์,เบ็ญจพร,สุดจิตต์"</formula1>
     </dataValidation>
-    <dataValidation sqref="M6:M400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="เลือกจากรายการเท่านั้น" type="list">
+    <dataValidation sqref="H6:H400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="เลือกจากรายการเท่านั้น" type="list">
+      <formula1>"SRI Corporation,สุธี,ธนากร,ธนวินท์,เบ็ญจพร,สุดจิตต์"</formula1>
+    </dataValidation>
+    <dataValidation sqref="N6:N400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="เลือกจากรายการเท่านั้น" type="list">
       <formula1>"ดำเนินอยู่,ไม่ได้ใช้,ขายแล้ว,ไถ่ถอนแล้ว"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2270,7 +2294,7 @@
       <formula1>"เงินกู้ธนาคาร,เงินกู้กรรมการ,เงินกู้ยืมอื่น,เงินมัดจำผู้เช่า,เจ้าหนี้ค้างจ่าย,ผลต่างรอกระทบยอด"</formula1>
     </dataValidation>
     <dataValidation sqref="C6:C400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="เลือกจากรายการเท่านั้น" type="list">
-      <formula1>"SRI Corporation,SRI Holding,SRI Capital,ธนากร,ธนวินท์,เบ็ญจพร"</formula1>
+      <formula1>"SRI Corporation,สุธี,ธนากร,ธนวินท์,เบ็ญจพร,สุดจิตต์"</formula1>
     </dataValidation>
     <dataValidation sqref="F6:F400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="เลือกจากรายการเท่านั้น" type="list">
       <formula1>"เดือน,ปี"</formula1>
@@ -2666,7 +2690,7 @@
       <formula1>"หุ้นไทย,หุ้น US,ETF,กองทุน,Crypto,ทองคำ,อื่นๆ"</formula1>
     </dataValidation>
     <dataValidation sqref="C6:C400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="เลือกจากรายการเท่านั้น" type="list">
-      <formula1>"SRI Corporation,SRI Holding,SRI Capital,ธนากร,ธนวินท์,เบ็ญจพร"</formula1>
+      <formula1>"SRI Corporation,สุธี,ธนากร,ธนวินท์,เบ็ญจพร,สุดจิตต์"</formula1>
     </dataValidation>
     <dataValidation sqref="F6:F400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="เลือกจากรายการเท่านั้น" type="list">
       <formula1>"THB,USD"</formula1>

--- a/templates/SRI_OS_ข้อมูลตั้งต้น.xlsx
+++ b/templates/SRI_OS_ข้อมูลตั้งต้น.xlsx
@@ -1394,7 +1394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1412,6 +1412,7 @@
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1481,25 +1482,30 @@
       </c>
       <c r="K4" s="13" t="inlineStr">
         <is>
+          <t>ค่ารีโนเวทสะสม</t>
+        </is>
+      </c>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
           <t>มูลค่าปัจจุบัน</t>
         </is>
       </c>
-      <c r="L4" s="13" t="inlineStr">
+      <c r="M4" s="13" t="inlineStr">
         <is>
           <t>แหล่งเงินทุน</t>
         </is>
       </c>
-      <c r="M4" s="13" t="inlineStr">
+      <c r="N4" s="13" t="inlineStr">
         <is>
           <t>วันที่ได้มา</t>
         </is>
       </c>
-      <c r="N4" s="12" t="inlineStr">
+      <c r="O4" s="12" t="inlineStr">
         <is>
           <t>สถานะ *</t>
         </is>
       </c>
-      <c r="O4" s="13" t="inlineStr">
+      <c r="P4" s="13" t="inlineStr">
         <is>
           <t>ผู้ดูแล</t>
         </is>
@@ -1553,30 +1559,35 @@
       </c>
       <c r="J5" s="14" t="inlineStr">
         <is>
-          <t>เงินที่จ่ายไปจริงทั้งหมด รวมค่าโอน</t>
+          <t>ราคาซื้อ + ค่าโอน · **ไม่รวมค่ารีโนเวท** (ช่องถัดไป) → เข้าบัญชี 1500</t>
         </is>
       </c>
       <c r="K5" s="14" t="inlineStr">
         <is>
+          <t>ที่บันทึกเป็นทุน ไม่ใช่ค่าซ่อมจร → เข้าบัญชี 1510 แยกจากต้นทุน</t>
+        </is>
+      </c>
+      <c r="L5" s="14" t="inlineStr">
+        <is>
           <t>ราคาประเมิน · **ต่ำกว่าต้นทุนได้** ถ้าราคาตก ไม่ต้องดัดให้เท่าทุน</t>
         </is>
       </c>
-      <c r="L5" s="14" t="inlineStr">
+      <c r="M5" s="14" t="inlineStr">
         <is>
           <t>เช่น ทุนป๊า / เงินหมุนจาก...</t>
         </is>
       </c>
-      <c r="M5" s="14" t="inlineStr">
+      <c r="N5" s="14" t="inlineStr">
         <is>
           <t>วว/ดด/ปปปป</t>
         </is>
       </c>
-      <c r="N5" s="14" t="inlineStr">
+      <c r="O5" s="14" t="inlineStr">
         <is>
           <t>ดำเนินอยู่ / ไม่ได้ใช้ / ขายแล้ว / ไถ่ถอนแล้ว</t>
         </is>
       </c>
-      <c r="O5" s="14" t="inlineStr">
+      <c r="P5" s="14" t="inlineStr">
         <is>
           <t>คนในทีมที่ดูแลทรัพย์นี้</t>
         </is>
@@ -1629,25 +1640,26 @@
       <c r="J6" s="15" t="n">
         <v>1800000</v>
       </c>
-      <c r="K6" s="15" t="n">
+      <c r="K6" s="15" t="inlineStr"/>
+      <c r="L6" s="15" t="n">
         <v>1800000</v>
       </c>
-      <c r="L6" s="15" t="inlineStr">
+      <c r="M6" s="15" t="inlineStr">
         <is>
           <t>เงินหมุนจากเปรมสิริ</t>
         </is>
       </c>
-      <c r="M6" s="15" t="inlineStr">
+      <c r="N6" s="15" t="inlineStr">
         <is>
           <t>02/12/2025</t>
         </is>
       </c>
-      <c r="N6" s="15" t="inlineStr">
+      <c r="O6" s="15" t="inlineStr">
         <is>
           <t>ดำเนินอยู่</t>
         </is>
       </c>
-      <c r="O6" s="15" t="inlineStr">
+      <c r="P6" s="15" t="inlineStr">
         <is>
           <t>วิน</t>
         </is>
@@ -1697,20 +1709,23 @@
         <v>2450000</v>
       </c>
       <c r="K7" s="15" t="n">
+        <v>185000</v>
+      </c>
+      <c r="L7" s="15" t="n">
         <v>2780000</v>
       </c>
-      <c r="L7" s="15" t="inlineStr"/>
-      <c r="M7" s="15" t="inlineStr">
+      <c r="M7" s="15" t="inlineStr"/>
+      <c r="N7" s="15" t="inlineStr">
         <is>
           <t>30/09/2025</t>
         </is>
       </c>
-      <c r="N7" s="15" t="inlineStr">
+      <c r="O7" s="15" t="inlineStr">
         <is>
           <t>ดำเนินอยู่</t>
         </is>
       </c>
-      <c r="O7" s="15" t="inlineStr">
+      <c r="P7" s="15" t="inlineStr">
         <is>
           <t>แพทตี้</t>
         </is>
@@ -1718,8 +1733,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A2:P2"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation sqref="C6:C400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="เลือกจากรายการเท่านั้น" type="list">
@@ -2490,205 +2505,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="56" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>พอร์ตหลักทรัพย์</t>
+          <t>พอร์ตหลักทรัพย์ — กรอกในไฟล์ 2 แทน</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>หุ้น กองทุน คริปโต ทอง · ต้นทุนใช้แบบถัวเฉลี่ย (Average cost) ตามที่ตั้งไว้ใน MVP</t>
+          <t>ชีทนี้ไม่ต้องกรอก · ลูกพี่เลือก FIFO จึงต้องรู้ต้นทุนรายล็อต ไม่ใช่ต้นทุนเฉลี่ย</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>ประเภท *</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>ชื่อ/รหัส *</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>ถือในชื่อ *</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>จำนวนหน่วย *</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>ต้นทุนเฉลี่ยต่อหน่วย *</t>
-        </is>
-      </c>
-      <c r="F4" s="12" t="inlineStr">
-        <is>
-          <t>สกุลเงิน *</t>
-        </is>
-      </c>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>ราคาล่าสุดต่อหน่วย</t>
-        </is>
-      </c>
-      <c r="H4" s="13" t="inlineStr">
-        <is>
-          <t>โบรกเกอร์</t>
-        </is>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>หมายเหตุ</t>
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>กรอกที่ไหนแทน</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>ทำไมต้องรายล็อต</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>ถ้ากรอกชีทนี้ไปแล้ว</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>หุ้นไทย / หุ้น US / ETF / กองทุน / Crypto / ทองคำ</t>
+          <t>ไฟล์ SRI_OS_2_ยอดตั้งต้นงบดุล.xlsx → ชีท 'พอร์ตลงทุน (รายล็อต)'</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>เช่น PTT, AAPL, SCBSET</t>
+          <t>FIFO ตัดต้นทุนล็อตที่ซื้อก่อนออกก่อน ค่าเฉลี่ยบอกไม่ได้ว่าล็อตไหนถูกตัด</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>ใครถือ</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>จำนวนหุ้น/หน่วย/กรัม</t>
-        </is>
-      </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>ราคาทุนเฉลี่ย</t>
-        </is>
-      </c>
-      <c r="F5" s="14" t="inlineStr">
-        <is>
-          <t>THB / USD</t>
-        </is>
-      </c>
-      <c r="G5" s="14" t="inlineStr">
-        <is>
-          <t>ถ้าไม่ใส่ ระบบจะดึงให้</t>
-        </is>
-      </c>
-      <c r="H5" s="14" t="inlineStr"/>
-      <c r="I5" s="14" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>หุ้นไทย</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>PTT</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>ธนากร</t>
-        </is>
-      </c>
-      <c r="D6" s="15" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E6" s="15" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="F6" s="15" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G6" s="15" t="n">
-        <v>36.25</v>
-      </c>
-      <c r="H6" s="15" t="inlineStr">
-        <is>
-          <t>SCBS</t>
-        </is>
-      </c>
-      <c r="I6" s="15" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>ทองคำ</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>ทองคำแท่ง 96.5%</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>ธนากร</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="n">
-        <v>100</v>
-      </c>
-      <c r="E7" s="15" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr"/>
-      <c r="H7" s="15" t="inlineStr">
-        <is>
-          <t>ห้างทอง</t>
-        </is>
-      </c>
-      <c r="I7" s="15" t="inlineStr">
-        <is>
-          <t>หน่วย = กรัม</t>
+          <t>ไม่เสียเปล่า — ยอดรวมใช้ตรวจทานกับชีทรายล็อตได้</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation sqref="A6:A400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="เลือกจากรายการเท่านั้น" type="list">
-      <formula1>"หุ้นไทย,หุ้น US,ETF,กองทุน,Crypto,ทองคำ,อื่นๆ"</formula1>
-    </dataValidation>
+  <dataValidations count="2">
     <dataValidation sqref="C6:C400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="เลือกจากรายการเท่านั้น" type="list">
       <formula1>"SRI Corporation,สุธี,ธนากร,ธนวินท์,เบ็ญจพร,สุดจิตต์"</formula1>
     </dataValidation>

--- a/templates/SRI_OS_ข้อมูลตั้งต้น.xlsx
+++ b/templates/SRI_OS_ข้อมูลตั้งต้น.xlsx
@@ -1741,7 +1741,7 @@
       <formula1>"Businesses,Real Estate,Paper Asset,Commodity &amp; Cash"</formula1>
     </dataValidation>
     <dataValidation sqref="D6:D400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="เลือกจากรายการเท่านั้น" type="list">
-      <formula1>"เงินลงทุนในกิจการ,บริษัทในเครือ,ปล่อยเช่า,รอขาย,โครงการระหว่างพัฒนา,รอปรับปรุง,ขายฝาก / รับจำนอง,หุ้น,ETF,กองทุน,พันธบัตร / หุ้นกู้,สัญญาเงินให้กู้ยืม,ทองคำ,คริปโต,เงินสดและเงินฝาก"</formula1>
+      <formula1>"เงินลงทุนในกิจการ,บริษัทในเครือ,ปล่อยเช่า,รอขาย,โครงการระหว่างพัฒนา,รอปรับปรุง,ขายฝาก / รับจำนอง,หุ้นในตลาดหลักทรัพย์,หุ้นบริษัทนอกตลาด,หุ้น (ยังไม่ระบุตลาด),ETF,กองทุน,พันธบัตร / หุ้นกู้,สัญญาเงินให้กู้ยืม,ทองคำ,สินทรัพย์ทางเลือกอื่น,คริปโต,เงินสดและเงินฝาก"</formula1>
     </dataValidation>
     <dataValidation sqref="G6:G400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="เลือกจากรายการเท่านั้น" type="list">
       <formula1>"SRI Corporation,สุธี,ธนากร,ธนวินท์,เบ็ญจพร,สุดจิตต์"</formula1>
